--- a/Outputs/Recycling_Plot_Data/ACCII/02_National_Stacked_2050_data_ACCII.xlsx
+++ b/Outputs/Recycling_Plot_Data/ACCII/02_National_Stacked_2050_data_ACCII.xlsx
@@ -351,7 +351,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E31"/>
+  <dimension ref="A1:D31"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -375,11 +375,6 @@
           <t>Tonnes</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
-        <is>
-          <t>pattern_type</t>
-        </is>
-      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -398,12 +393,7 @@
         </is>
       </c>
       <c r="D2">
-        <v>2.09640923357902</v>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>stripe</t>
-        </is>
+        <v>1.877644952198894</v>
       </c>
     </row>
     <row r="3">
@@ -423,12 +413,7 @@
         </is>
       </c>
       <c r="D3">
-        <v>1.39743929871637</v>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>stripe</t>
-        </is>
+        <v>1.0292777328604</v>
       </c>
     </row>
     <row r="4">
@@ -448,12 +433,7 @@
         </is>
       </c>
       <c r="D4">
-        <v>0.829535854934079</v>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>stripe</t>
-        </is>
+        <v>0.7496032910202518</v>
       </c>
     </row>
     <row r="5">
@@ -473,12 +453,7 @@
         </is>
       </c>
       <c r="D5">
-        <v>0.548836715476051</v>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>stripe</t>
-        </is>
+        <v>0.413464627302696</v>
       </c>
     </row>
     <row r="6">
@@ -498,12 +473,7 @@
         </is>
       </c>
       <c r="D6">
-        <v>1.55336015106285</v>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>stripe</t>
-        </is>
+        <v>1.403681196479397</v>
       </c>
     </row>
     <row r="7">
@@ -523,12 +493,7 @@
         </is>
       </c>
       <c r="D7">
-        <v>1.02773265096355</v>
-      </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>stripe</t>
-        </is>
+        <v>0.774239560720494</v>
       </c>
     </row>
     <row r="8">
@@ -548,12 +513,7 @@
         </is>
       </c>
       <c r="D8">
-        <v>1.29044808536268</v>
-      </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>stripe</t>
-        </is>
+        <v>1.059588203064264</v>
       </c>
     </row>
     <row r="9">
@@ -573,12 +533,7 @@
         </is>
       </c>
       <c r="D9">
-        <v>0.913946657654751</v>
-      </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>stripe</t>
-        </is>
+        <v>0.6288445391991137</v>
       </c>
     </row>
     <row r="10">
@@ -600,11 +555,6 @@
       <c r="D10">
         <v>0.318</v>
       </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>stripe</t>
-        </is>
-      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -625,11 +575,6 @@
       <c r="D11">
         <v>0.2825</v>
       </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>stripe</t>
-        </is>
-      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -648,12 +593,7 @@
         </is>
       </c>
       <c r="D12">
-        <v>0.174481822043239</v>
-      </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>circle</t>
-        </is>
+        <v>0.1102453453840367</v>
       </c>
     </row>
     <row r="13">
@@ -673,12 +613,7 @@
         </is>
       </c>
       <c r="D13">
-        <v>0.174481822043239</v>
-      </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>circle</t>
-        </is>
+        <v>0.06637732855497551</v>
       </c>
     </row>
     <row r="14">
@@ -698,12 +633,7 @@
         </is>
       </c>
       <c r="D14">
-        <v>0.0959590205072049</v>
-      </c>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t>circle</t>
-        </is>
+        <v>0.08671258408835963</v>
       </c>
     </row>
     <row r="15">
@@ -723,12 +653,7 @@
         </is>
       </c>
       <c r="D15">
-        <v>0.0634883149682042</v>
-      </c>
-      <c r="E15" t="inlineStr">
-        <is>
-          <t>circle</t>
-        </is>
+        <v>0.04782874714137119</v>
       </c>
     </row>
     <row r="16">
@@ -750,11 +675,6 @@
       <c r="D16">
         <v>0</v>
       </c>
-      <c r="E16" t="inlineStr">
-        <is>
-          <t>circle</t>
-        </is>
-      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -775,11 +695,6 @@
       <c r="D17">
         <v>0</v>
       </c>
-      <c r="E17" t="inlineStr">
-        <is>
-          <t>circle</t>
-        </is>
-      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -798,12 +713,7 @@
         </is>
       </c>
       <c r="D18">
-        <v>0.654099500848064</v>
-      </c>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t>circle</t>
-        </is>
+        <v>0.6659696282424172</v>
       </c>
     </row>
     <row r="19">
@@ -823,12 +733,7 @@
         </is>
       </c>
       <c r="D19">
-        <v>0.398976704677351</v>
-      </c>
-      <c r="E19" t="inlineStr">
-        <is>
-          <t>circle</t>
-        </is>
+        <v>0.3939349635357499</v>
       </c>
     </row>
     <row r="20">
@@ -850,11 +755,6 @@
       <c r="D20">
         <v>0</v>
       </c>
-      <c r="E20" t="inlineStr">
-        <is>
-          <t>circle</t>
-        </is>
-      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -875,11 +775,6 @@
       <c r="D21">
         <v>0</v>
       </c>
-      <c r="E21" t="inlineStr">
-        <is>
-          <t>circle</t>
-        </is>
-      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -898,12 +793,7 @@
         </is>
       </c>
       <c r="D22">
-        <v>13.1929226990304</v>
-      </c>
-      <c r="E22" t="inlineStr">
-        <is>
-          <t>diagonal</t>
-        </is>
+        <v>11.81286824521793</v>
       </c>
     </row>
     <row r="23">
@@ -923,12 +813,7 @@
         </is>
       </c>
       <c r="D23">
-        <v>8.87460096541043</v>
-      </c>
-      <c r="E23" t="inlineStr">
-        <is>
-          <t>diagonal</t>
-        </is>
+        <v>6.536850974819679</v>
       </c>
     </row>
     <row r="24">
@@ -948,12 +833,7 @@
         </is>
       </c>
       <c r="D24">
-        <v>13.8736569322164</v>
-      </c>
-      <c r="E24" t="inlineStr">
-        <is>
-          <t>diagonal</t>
-        </is>
+        <v>12.53681662223244</v>
       </c>
     </row>
     <row r="25">
@@ -973,12 +853,7 @@
         </is>
       </c>
       <c r="D25">
-        <v>9.179075572235879</v>
-      </c>
-      <c r="E25" t="inlineStr">
-        <is>
-          <t>diagonal</t>
-        </is>
+        <v>6.915031289708594</v>
       </c>
     </row>
     <row r="26">
@@ -998,12 +873,7 @@
         </is>
       </c>
       <c r="D26">
-        <v>7.78934953170064</v>
-      </c>
-      <c r="E26" t="inlineStr">
-        <is>
-          <t>diagonal</t>
-        </is>
+        <v>7.038781999765233</v>
       </c>
     </row>
     <row r="27">
@@ -1023,12 +893,7 @@
         </is>
       </c>
       <c r="D27">
-        <v>5.15358195458981</v>
-      </c>
-      <c r="E27" t="inlineStr">
-        <is>
-          <t>diagonal</t>
-        </is>
+        <v>3.882436764967768</v>
       </c>
     </row>
     <row r="28">
@@ -1048,12 +913,7 @@
         </is>
       </c>
       <c r="D28">
-        <v>7.8238695018128</v>
-      </c>
-      <c r="E28" t="inlineStr">
-        <is>
-          <t>diagonal</t>
-        </is>
+        <v>6.350599542722977</v>
       </c>
     </row>
     <row r="29">
@@ -1073,12 +933,7 @@
         </is>
       </c>
       <c r="D29">
-        <v>5.66706171192233</v>
-      </c>
-      <c r="E29" t="inlineStr">
-        <is>
-          <t>diagonal</t>
-        </is>
+        <v>3.813774874015224</v>
       </c>
     </row>
     <row r="30">
@@ -1100,11 +955,6 @@
       <c r="D30">
         <v>0.60038736185</v>
       </c>
-      <c r="E30" t="inlineStr">
-        <is>
-          <t>diagonal</t>
-        </is>
-      </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -1124,11 +974,6 @@
       </c>
       <c r="D31">
         <v>1.120380881403</v>
-      </c>
-      <c r="E31" t="inlineStr">
-        <is>
-          <t>diagonal</t>
-        </is>
       </c>
     </row>
   </sheetData>
